--- a/Instagram Analystics.xlsx
+++ b/Instagram Analystics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFF0852-ADDE-4EF7-A7EC-D12FDC0CAEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65767A66-3618-4619-A60E-BF2F06BE9D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8089" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8094" uniqueCount="713">
   <si>
     <t>Post_ID</t>
   </si>
@@ -2180,12 +2180,15 @@
   <si>
     <t>Details for Average of Shares</t>
   </si>
+  <si>
+    <t>Instagram Engagement Analytics Dashboard</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2197,6 +2200,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2237,7 +2248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2249,11 +2260,74 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="55">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -2675,22 +2749,22 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>372</c:v>
+                  <c:v>429.87777777777779</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>494.83333333333331</c:v>
+                  <c:v>443.7831325301205</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>428.46666666666664</c:v>
+                  <c:v>490.89333333333332</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>373.8235294117647</c:v>
+                  <c:v>452.76470588235293</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>282.38888888888891</c:v>
+                  <c:v>365.8279569892473</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>492.07692307692309</c:v>
+                  <c:v>470.2837837837838</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2953,12 +3027,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -2973,20 +3044,64 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent2"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
+          <a:ln w="34925" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+              <a:schemeClr val="accent2"/>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent2"/>
             </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3004,127 +3119,9 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent2"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="lt1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3166,36 +3163,77 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent2"/>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
+              <a:ln w="22225">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$53:$A$54</c:f>
+              <c:f>Sheet1!$A$53:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$53:$B$54</c:f>
+              <c:f>Sheet1!$B$53:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>47446</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>57572</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>59825</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>73993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>81542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3215,6 +3253,28 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1"/>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="lt1">
+                      <a:alpha val="0"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="648187568"/>
         <c:axId val="608186800"/>
@@ -3232,12 +3292,9 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -3248,12 +3305,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3277,20 +3331,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3309,10 +3349,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3351,10 +3388,7 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -3378,14 +3412,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="accent2"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -3856,16 +3887,16 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>205</c:v>
+                  <c:v>1335</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>188</c:v>
+                  <c:v>1005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>430</c:v>
+                  <c:v>2539</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>57</c:v>
+                  <c:v>258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4222,28 +4253,28 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>6683.2142857142853</c:v>
+                  <c:v>6673.7910447761196</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5591.833333333333</c:v>
+                  <c:v>5692.322580645161</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5842.8125</c:v>
+                  <c:v>5612.169230769231</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5469.5384615384619</c:v>
+                  <c:v>5501.6417910447763</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3741.7</c:v>
+                  <c:v>5538.2615384615383</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4105.5</c:v>
+                  <c:v>5421.507246376812</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6134.5</c:v>
+                  <c:v>5896.9245283018872</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5618.3571428571431</c:v>
+                  <c:v>5903.3653846153848</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4614,23 +4645,47 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$53:$A$54</c:f>
+              <c:f>Sheet1!$A$53:$A$58</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$53:$B$54</c:f>
+              <c:f>Sheet1!$B$53:$B$58</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>47446</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>57572</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>59825</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>73993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>81542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5169,28 +5224,28 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>8661.2999999999993</c:v>
+                  <c:v>10923.692307692309</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7836.4285714285716</c:v>
+                  <c:v>10049.742424242424</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14813.777777777777</c:v>
+                  <c:v>10607.953846153847</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12746.333333333334</c:v>
+                  <c:v>10634.416666666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9302</c:v>
+                  <c:v>10626.672131147541</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9568</c:v>
+                  <c:v>10612.171875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6371.125</c:v>
+                  <c:v>8958.8196721311469</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12433</c:v>
+                  <c:v>10317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5911,22 +5966,22 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>372</c:v>
+                  <c:v>429.87777777777779</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>494.83333333333331</c:v>
+                  <c:v>443.7831325301205</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>428.46666666666664</c:v>
+                  <c:v>490.89333333333332</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>373.8235294117647</c:v>
+                  <c:v>452.76470588235293</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>282.38888888888891</c:v>
+                  <c:v>365.8279569892473</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>492.07692307692309</c:v>
+                  <c:v>470.2837837837838</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6164,10 +6219,10 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="104"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="4"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
@@ -6211,9 +6266,9 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6275,9 +6330,9 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6294,9 +6349,9 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6313,9 +6368,9 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6332,9 +6387,9 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6351,9 +6406,9 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6415,9 +6470,9 @@
         <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6434,9 +6489,9 @@
         <c:idx val="7"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6453,9 +6508,9 @@
         <c:idx val="8"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6472,9 +6527,9 @@
         <c:idx val="9"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="25400">
+          <a:ln w="19050">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -6491,7 +6546,7 @@
         <c:idx val="10"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -6555,7 +6610,7 @@
         <c:idx val="11"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -6574,7 +6629,7 @@
         <c:idx val="12"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -6593,7 +6648,7 @@
         <c:idx val="13"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -6612,7 +6667,7 @@
         <c:idx val="14"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -6690,7 +6745,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent2">
+                  <a:shade val="58000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -6715,7 +6772,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent2">
+                  <a:shade val="86000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -6740,7 +6799,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent2">
+                  <a:tint val="86000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -6765,7 +6826,9 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent2">
+                  <a:tint val="58000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -6868,16 +6931,16 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>205</c:v>
+                  <c:v>1335</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>188</c:v>
+                  <c:v>1005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>430</c:v>
+                  <c:v>2539</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>57</c:v>
+                  <c:v>258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7030,12 +7093,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -7050,52 +7110,8 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent2"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
@@ -7110,52 +7126,8 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent2"/>
-          </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
@@ -7171,21 +7143,37 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
-          <a:ln w="28575" cap="rnd">
+          <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+              <a:schemeClr val="accent2"/>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="14"/>
+          <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent2"/>
             </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
           <c:spPr>
-            <a:noFill/>
+            <a:solidFill>
+              <a:srgbClr val="C0504D"/>
+            </a:solidFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -7198,12 +7186,9 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="lt1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -7213,7 +7198,7 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="t"/>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -7246,20 +7231,36 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent2"/>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="14"/>
+            <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:spPr>
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
@@ -7272,12 +7273,9 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="lt1"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -7287,7 +7285,7 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -7300,14 +7298,13 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
+                        <a:schemeClr val="accent2">
+                          <a:lumMod val="60000"/>
+                          <a:lumOff val="40000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -7354,28 +7351,28 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>6683.2142857142853</c:v>
+                  <c:v>6673.7910447761196</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5591.833333333333</c:v>
+                  <c:v>5692.322580645161</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5842.8125</c:v>
+                  <c:v>5612.169230769231</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5469.5384615384619</c:v>
+                  <c:v>5501.6417910447763</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3741.7</c:v>
+                  <c:v>5538.2615384615383</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4105.5</c:v>
+                  <c:v>5421.507246376812</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6134.5</c:v>
+                  <c:v>5896.9245283018872</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5618.3571428571431</c:v>
+                  <c:v>5903.3653846153848</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7388,7 +7385,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -7396,6 +7393,28 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1"/>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="lt1">
+                      <a:alpha val="0"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="642000864"/>
         <c:axId val="608301040"/>
@@ -7413,14 +7432,8 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -7429,12 +7442,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="30" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="lt1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -7456,53 +7466,12 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="642000864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -7532,10 +7501,7 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -7559,13 +7525,12 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -7658,165 +7623,9 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent2">
-                  <a:shade val="51000"/>
-                  <a:satMod val="130000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="80000">
-                <a:schemeClr val="accent2">
-                  <a:shade val="93000"/>
-                  <a:satMod val="130000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent2">
-                  <a:shade val="94000"/>
-                  <a:satMod val="135000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent2">
-                  <a:shade val="51000"/>
-                  <a:satMod val="130000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="80000">
-                <a:schemeClr val="accent2">
-                  <a:shade val="93000"/>
-                  <a:satMod val="130000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent2">
-                  <a:shade val="94000"/>
-                  <a:satMod val="135000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
@@ -7867,7 +7676,57 @@
           </a:sp3d>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent2">
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -8077,28 +7936,28 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>8661.2999999999993</c:v>
+                  <c:v>10923.692307692309</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7836.4285714285716</c:v>
+                  <c:v>10049.742424242424</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14813.777777777777</c:v>
+                  <c:v>10607.953846153847</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12746.333333333334</c:v>
+                  <c:v>10634.416666666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9302</c:v>
+                  <c:v>10626.672131147541</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9568</c:v>
+                  <c:v>10612.171875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6371.125</c:v>
+                  <c:v>8958.8196721311469</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12433</c:v>
+                  <c:v>10317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8591,42 +8450,8 @@
 </file>
 
 <file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -9207,59 +9032,53 @@
 </file>
 
 <file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="229">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" spc="100" baseline="0"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -9271,22 +9090,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9294,10 +9109,7 @@
       </a:solidFill>
       <a:ln>
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -9308,71 +9120,87 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
     </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="22225">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
@@ -9381,10 +9209,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -9396,31 +9224,30 @@
     </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -9429,15 +9256,15 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9448,37 +9275,51 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
   <cs:errorBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:errorBar>
   <cs:floor>
@@ -9486,28 +9327,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9515,59 +9351,62 @@
     </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -9576,57 +9415,67 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -9635,28 +9484,25 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
+    <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -9665,15 +9511,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -9681,13 +9526,15 @@
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9698,10 +9545,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -9710,14 +9554,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -12797,58 +12635,46 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="238">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" spc="30" baseline="0"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -12858,25 +12684,28 @@
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <cs:styleClr val="auto"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -12884,10 +12713,7 @@
       </a:solidFill>
       <a:ln>
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -12898,83 +12724,93 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
     </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="14"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -12986,31 +12822,30 @@
     </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -13019,15 +12854,15 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -13038,37 +12873,51 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
   <cs:errorBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:errorBar>
   <cs:floor>
@@ -13076,28 +12925,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -13105,59 +12949,62 @@
     </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -13166,57 +13013,56 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -13225,28 +13071,25 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
+    <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -13255,15 +13098,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
@@ -13271,13 +13113,15 @@
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -13288,10 +13132,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -13300,14 +13141,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -14160,15 +13995,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>600074</xdr:colOff>
+      <xdr:colOff>600073</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>152399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>595311</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>151533</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>102052</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -14183,12 +14018,24 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="600074" y="152399"/>
-          <a:ext cx="7920037" cy="380134"/>
+          <a:off x="600073" y="152399"/>
+          <a:ext cx="10523765" cy="408896"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -14212,10 +14059,10 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-IN" sz="1400" b="1"/>
+            <a:rPr lang="en-IN" sz="1600" b="1"/>
             <a:t>Instagram Engagement Analytics Dashboard</a:t>
           </a:r>
-          <a:endParaRPr lang="en-IN" sz="1400" b="1">
+          <a:endParaRPr lang="en-IN" sz="1600" b="1">
             <a:latin typeface="+mj-lt"/>
           </a:endParaRPr>
         </a:p>
@@ -14226,15 +14073,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>596718</xdr:colOff>
+      <xdr:colOff>596717</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>165992</xdr:rowOff>
+      <xdr:rowOff>117994</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>516721</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>458610</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>61489</xdr:rowOff>
+      <xdr:rowOff>155510</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Sheet4!A4">
       <xdr:nvSpPr>
@@ -14249,12 +14096,24 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="596718" y="741922"/>
-          <a:ext cx="1758550" cy="471427"/>
+          <a:off x="596717" y="701157"/>
+          <a:ext cx="2272301" cy="620680"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -14273,22 +14132,49 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="b"/>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Total Post </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
           <a:fld id="{5747E6BC-12B3-496C-A685-D36FE3E5BEEA}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1400" b="1">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>500</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1100"/>
+          <a:endParaRPr lang="en-US" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -14296,16 +14182,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>192936</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>41286</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>582083</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>117593</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>542395</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>66146</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>211667</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>23518</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14334,16 +14220,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>14653</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>367432</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>146538</xdr:rowOff>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>285120</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>329260</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>11759</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14373,15 +14259,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:colOff>571501</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>175847</xdr:rowOff>
+      <xdr:rowOff>107540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>278423</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>46090</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>29309</xdr:rowOff>
+      <xdr:rowOff>158361</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14410,16 +14296,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>556846</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>43961</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>493889</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>108239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>87922</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>73268</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>167569</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14448,16 +14334,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>595313</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176781</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>136815</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114305</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>529167</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>26458</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>70670</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>122903</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14486,16 +14372,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>498231</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>146539</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>199719</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>112741</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>582247</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>29308</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>168993</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>122903</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -14531,8 +14417,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6594231" y="1480039"/>
-              <a:ext cx="1912816" cy="1978269"/>
+              <a:off x="9417461" y="3492580"/>
+              <a:ext cx="1812822" cy="2038065"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -14564,16 +14450,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>483577</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>170175</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>161193</xdr:rowOff>
+      <xdr:rowOff>115104</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>554891</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>61453</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>29309</xdr:rowOff>
+      <xdr:rowOff>138266</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -14609,8 +14495,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6579577" y="3590193"/>
-              <a:ext cx="1900114" cy="1963616"/>
+              <a:off x="8158885" y="3494943"/>
+              <a:ext cx="1120310" cy="2051065"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -14642,16 +14528,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>25144</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>305741</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>174040</xdr:rowOff>
+      <xdr:rowOff>142842</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>548398</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>152871</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>69537</xdr:rowOff>
+      <xdr:rowOff>203989</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Sheet4!B4">
       <xdr:nvSpPr>
@@ -14666,12 +14552,24 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2438144" y="745540"/>
-          <a:ext cx="1729754" cy="466997"/>
+          <a:off x="3318751" y="726005"/>
+          <a:ext cx="2257538" cy="644311"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -14690,22 +14588,49 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="b"/>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Avg Share</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
           <a:fld id="{C3895E56-5949-4297-A7C0-0C34473712F8}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1400" b="1">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>69.858</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1100"/>
+          <a:endParaRPr lang="en-US" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -14713,16 +14638,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>104519</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1406</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>142290</xdr:rowOff>
+      <xdr:rowOff>118084</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>24522</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>458611</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>37787</xdr:rowOff>
+      <xdr:rowOff>174949</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Sheet4!C4">
       <xdr:nvSpPr>
@@ -14737,12 +14662,24 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4327269" y="713790"/>
-          <a:ext cx="1729753" cy="466997"/>
+          <a:off x="6027426" y="701247"/>
+          <a:ext cx="2265012" cy="640029"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -14761,22 +14698,49 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="b"/>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Max Saves</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
           <a:fld id="{F0A1A96E-ACA8-4434-B1A8-B0CD59ADDFF2}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1400" b="1">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>583</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1100"/>
+          <a:endParaRPr lang="en-US" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -14784,16 +14748,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>209294</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>295431</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>135940</xdr:rowOff>
+      <xdr:rowOff>118856</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>129297</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>129351</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>31437</xdr:rowOff>
+      <xdr:rowOff>184355</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="Sheet4!D4">
       <xdr:nvSpPr>
@@ -14808,12 +14772,24 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6241794" y="707440"/>
-          <a:ext cx="1729753" cy="466997"/>
+          <a:off x="8898657" y="671921"/>
+          <a:ext cx="2291984" cy="618563"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -14832,22 +14808,49 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="b"/>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Avg Reach </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
           <a:fld id="{579F125D-1593-4C41-9137-B4EBD302054A}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1400" b="1">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
+            <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:t>5774.104</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-US" sz="1100"/>
+          <a:endParaRPr lang="en-US" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -27366,11 +27369,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -27819,7 +27822,7 @@
     <dataField name="Average of Likes" fld="15" subtotal="average" baseField="5" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="54">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -27856,19 +27859,19 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4CCEEBDF-9F97-4311-93E8-548CA4E8067E}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30">
-  <location ref="A52:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4CCEEBDF-9F97-4311-93E8-548CA4E8067E}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="32">
+  <location ref="A52:B58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -28307,9 +28310,21 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -28322,7 +28337,7 @@
     <dataField name="Sum of Total_Engagement" fld="19" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="50">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -28359,7 +28374,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE992A46-BC49-49B2-9770-9EC3E82FFC00}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="29">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE992A46-BC49-49B2-9770-9EC3E82FFC00}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="31">
   <location ref="A37:B46" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -28367,11 +28382,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -28846,7 +28861,7 @@
     <dataField name="Average of Impressions" fld="14" subtotal="average" baseField="7" baseItem="3"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="51">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -28883,7 +28898,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{19421DA0-AAEE-4735-A82E-B68B783EF07A}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{19421DA0-AAEE-4735-A82E-B68B783EF07A}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="29">
   <location ref="A26:B35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -28891,11 +28906,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -29370,7 +29385,7 @@
     <dataField name="Average of Reach" fld="13" subtotal="average" baseField="6" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="52">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -29407,7 +29422,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05DC5213-CA40-454B-A319-B919AACB165C}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05DC5213-CA40-454B-A319-B919AACB165C}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
   <location ref="A14:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -29415,11 +29430,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -29870,7 +29885,7 @@
     <dataField name="Sum of Followers_Gained" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="53">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -32218,11 +32233,11 @@
   <data>
     <tabular pivotCacheId="89043975">
       <items count="5">
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="1" s="1"/>
-        <i x="2"/>
-        <i x="3"/>
-        <i x="4"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
       </items>
     </tabular>
   </data>
@@ -32582,7 +32597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D89778-9B70-457E-861D-F3E9FDA7D681}">
-  <dimension ref="A3:B54"/>
+  <dimension ref="A3:B58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -32607,7 +32622,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="4">
-        <v>372</v>
+        <v>429.87777777777779</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -32615,7 +32630,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="4">
-        <v>494.83333333333331</v>
+        <v>443.7831325301205</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -32623,7 +32638,7 @@
         <v>71</v>
       </c>
       <c r="B6" s="4">
-        <v>428.46666666666664</v>
+        <v>490.89333333333332</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -32631,7 +32646,7 @@
         <v>31</v>
       </c>
       <c r="B7" s="4">
-        <v>373.8235294117647</v>
+        <v>452.76470588235293</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -32639,7 +32654,7 @@
         <v>36</v>
       </c>
       <c r="B8" s="4">
-        <v>282.38888888888891</v>
+        <v>365.8279569892473</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -32647,7 +32662,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="4">
-        <v>492.07692307692309</v>
+        <v>470.2837837837838</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -32655,7 +32670,7 @@
         <v>702</v>
       </c>
       <c r="B10" s="4">
-        <v>403.96842105263158</v>
+        <v>439.29599999999999</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -32671,7 +32686,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="4">
-        <v>205</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -32679,7 +32694,7 @@
         <v>67</v>
       </c>
       <c r="B16" s="4">
-        <v>188</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -32687,7 +32702,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="4">
-        <v>430</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -32695,7 +32710,7 @@
         <v>30</v>
       </c>
       <c r="B18" s="4">
-        <v>57</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -32703,7 +32718,7 @@
         <v>702</v>
       </c>
       <c r="B19" s="4">
-        <v>880</v>
+        <v>5137</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -32719,7 +32734,7 @@
         <v>60</v>
       </c>
       <c r="B27" s="4">
-        <v>6683.2142857142853</v>
+        <v>6673.7910447761196</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -32727,7 +32742,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="4">
-        <v>5591.833333333333</v>
+        <v>5692.322580645161</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -32735,7 +32750,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="4">
-        <v>5842.8125</v>
+        <v>5612.169230769231</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -32743,7 +32758,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="4">
-        <v>5469.5384615384619</v>
+        <v>5501.6417910447763</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -32751,7 +32766,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="4">
-        <v>3741.7</v>
+        <v>5538.2615384615383</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -32759,7 +32774,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="4">
-        <v>4105.5</v>
+        <v>5421.507246376812</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -32767,7 +32782,7 @@
         <v>48</v>
       </c>
       <c r="B33" s="4">
-        <v>6134.5</v>
+        <v>5896.9245283018872</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -32775,7 +32790,7 @@
         <v>84</v>
       </c>
       <c r="B34" s="4">
-        <v>5618.3571428571431</v>
+        <v>5903.3653846153848</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -32783,7 +32798,7 @@
         <v>702</v>
       </c>
       <c r="B35" s="4">
-        <v>5465.1789473684212</v>
+        <v>5774.1040000000003</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -32799,7 +32814,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="4">
-        <v>8661.2999999999993</v>
+        <v>10923.692307692309</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -32807,7 +32822,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="4">
-        <v>7836.4285714285716</v>
+        <v>10049.742424242424</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -32815,7 +32830,7 @@
         <v>62</v>
       </c>
       <c r="B40" s="4">
-        <v>14813.777777777777</v>
+        <v>10607.953846153847</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -32823,7 +32838,7 @@
         <v>28</v>
       </c>
       <c r="B41" s="4">
-        <v>12746.333333333334</v>
+        <v>10634.416666666666</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -32831,7 +32846,7 @@
         <v>85</v>
       </c>
       <c r="B42" s="4">
-        <v>9302</v>
+        <v>10626.672131147541</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -32839,7 +32854,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="4">
-        <v>9568</v>
+        <v>10612.171875</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -32847,7 +32862,7 @@
         <v>88</v>
       </c>
       <c r="B44" s="4">
-        <v>6371.125</v>
+        <v>8958.8196721311469</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -32855,7 +32870,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="4">
-        <v>12433</v>
+        <v>10317</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -32863,7 +32878,7 @@
         <v>702</v>
       </c>
       <c r="B46" s="4">
-        <v>10001.768421052631</v>
+        <v>10338.214</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -32876,18 +32891,50 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>185</v>
+        <v>24</v>
       </c>
       <c r="B53" s="4">
-        <v>57572</v>
+        <v>47446</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>702</v>
+        <v>185</v>
       </c>
       <c r="B54" s="4">
         <v>57572</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B55" s="4">
+        <v>59825</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B56" s="4">
+        <v>73993</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B57" s="4">
+        <v>81542</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B58" s="4">
+        <v>320378</v>
       </c>
     </row>
   </sheetData>
@@ -32905,9 +32952,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C5A744-8FBF-4359-ADB2-943500F77532}">
-  <dimension ref="A1"/>
+  <dimension ref="P7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="7" spans="16:16" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="P7" s="7" t="s">
+        <v>712</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <extLst>
